--- a/Configs/GameConfig/Datas/fg/#RaidCounter-突袭反制.xlsx
+++ b/Configs/GameConfig/Datas/fg/#RaidCounter-突袭反制.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>swarm</t>
+          <t>deflect</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">

--- a/Configs/GameConfig/Datas/fg/#RaidCounter-突袭反制.xlsx
+++ b/Configs/GameConfig/Datas/fg/#RaidCounter-突袭反制.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -830,6 +830,114 @@
         <v>2.5</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr"/>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>clarity.fluid</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>clarity</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>fluid</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>cryo</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>raid.counter.clarity.fluid.name</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>raid.counter.clarity.fluid.desc</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr"/>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>clarity.fuse</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>clarity</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>fuse</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>swarm</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>raid.counter.clarity.fuse.name</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>raid.counter.clarity.fuse.desc</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr"/>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>clarity.em</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>clarity</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>em</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>insulated</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>raid.counter.clarity.em.name</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>raid.counter.clarity.em.desc</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
